--- a/Compititor's_Price/Rockwool_Prices/Rockwool_Prices_23-09-2025.xlsx
+++ b/Compititor's_Price/Rockwool_Prices/Rockwool_Prices_23-09-2025.xlsx
@@ -538,34 +538,8 @@
           <t>N/L</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Error: Message: 
-Stacktrace:
-	GetHandleVerifier [0x0xd40c13+66051]
-	GetHandleVerifier [0x0xd40c54+66116]
-	(No symbol) [0x0xb1db33]
-	(No symbol) [0x0xb678a8]
-	(No symbol) [0x0xb67c4b]
-	(No symbol) [0x0xbae0a2]
-	(No symbol) [0x0xb89fd4]
-	(No symbol) [0x0xbab7f1]
-	(No symbol) [0x0xb89d86]
-	(No symbol) [0x0xb5b53e]
-	(No symbol) [0x0xb5c414]
-	GetHandleVerifier [0x0xf88a13+2457603]
-	GetHandleVerifier [0x0xf839d2+2437058]
-	GetHandleVerifier [0x0xd697f2+232930]
-	GetHandleVerifier [0x0xd59a18+167944]
-	GetHandleVerifier [0x0xd6092d+196381]
-	GetHandleVerifier [0x0xd48ee8+99544]
-	GetHandleVerifier [0x0xd49082+99954]
-	GetHandleVerifier [0x0xd3322a+10266]
-	BaseThreadInitThunk [0x0x761f5d49+25]
-	RtlInitializeExceptionChain [0x0x7725d6db+107]
-	RtlGetAppContainerNamedObjectPath [0x0x7725d661+561]
-</t>
-        </is>
+      <c r="E4" t="n">
+        <v>962.16</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -595,34 +569,8 @@
           <t>N/L</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Error: Message: 
-Stacktrace:
-	GetHandleVerifier [0x0xd40c13+66051]
-	GetHandleVerifier [0x0xd40c54+66116]
-	(No symbol) [0x0xb1db33]
-	(No symbol) [0x0xb678a8]
-	(No symbol) [0x0xb67c4b]
-	(No symbol) [0x0xbae0a2]
-	(No symbol) [0x0xb89fd4]
-	(No symbol) [0x0xbab7f1]
-	(No symbol) [0x0xb89d86]
-	(No symbol) [0x0xb5b53e]
-	(No symbol) [0x0xb5c414]
-	GetHandleVerifier [0x0xf88a13+2457603]
-	GetHandleVerifier [0x0xf839d2+2437058]
-	GetHandleVerifier [0x0xd697f2+232930]
-	GetHandleVerifier [0x0xd59a18+167944]
-	GetHandleVerifier [0x0xd6092d+196381]
-	GetHandleVerifier [0x0xd48ee8+99544]
-	GetHandleVerifier [0x0xd49082+99954]
-	GetHandleVerifier [0x0xd3322a+10266]
-	BaseThreadInitThunk [0x0x761f5d49+25]
-	RtlInitializeExceptionChain [0x0x7725d6db+107]
-	RtlGetAppContainerNamedObjectPath [0x0x7725d661+561]
-</t>
-        </is>
+      <c r="E5" t="n">
+        <v>80.18000000000001</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -931,7 +879,7 @@
         <v>1166.95</v>
       </c>
       <c r="E14" t="n">
-        <v>1031.76</v>
+        <v>1067.76</v>
       </c>
       <c r="F14" t="n">
         <v>1127.88</v>
@@ -958,7 +906,7 @@
         <v>89.15000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>85.98</v>
+        <v>88.98</v>
       </c>
       <c r="F15" t="n">
         <v>93.98999999999999</v>
@@ -986,34 +934,8 @@
           <t>N/L</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Error: Message: 
-Stacktrace:
-	GetHandleVerifier [0x0xd40c13+66051]
-	GetHandleVerifier [0x0xd40c54+66116]
-	(No symbol) [0x0xb1db33]
-	(No symbol) [0x0xb678a8]
-	(No symbol) [0x0xb67c4b]
-	(No symbol) [0x0xbae0a2]
-	(No symbol) [0x0xb89fd4]
-	(No symbol) [0x0xbab7f1]
-	(No symbol) [0x0xb89d86]
-	(No symbol) [0x0xb5b53e]
-	(No symbol) [0x0xb5c414]
-	GetHandleVerifier [0x0xf88a13+2457603]
-	GetHandleVerifier [0x0xf839d2+2437058]
-	GetHandleVerifier [0x0xd697f2+232930]
-	GetHandleVerifier [0x0xd59a18+167944]
-	GetHandleVerifier [0x0xd6092d+196381]
-	GetHandleVerifier [0x0xd48ee8+99544]
-	GetHandleVerifier [0x0xd49082+99954]
-	GetHandleVerifier [0x0xd3322a+10266]
-	BaseThreadInitThunk [0x0x761f5d49+25]
-	RtlInitializeExceptionChain [0x0x7725d6db+107]
-	RtlGetAppContainerNamedObjectPath [0x0x7725d661+561]
-</t>
-        </is>
+      <c r="E16" t="n">
+        <v>1148.04</v>
       </c>
       <c r="F16" t="n">
         <v>1019.88</v>
@@ -1041,34 +963,8 @@
           <t>N/L</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Error: Message: 
-Stacktrace:
-	GetHandleVerifier [0x0xd40c13+66051]
-	GetHandleVerifier [0x0xd40c54+66116]
-	(No symbol) [0x0xb1db33]
-	(No symbol) [0x0xb678a8]
-	(No symbol) [0x0xb67c4b]
-	(No symbol) [0x0xbae0a2]
-	(No symbol) [0x0xb89fd4]
-	(No symbol) [0x0xbab7f1]
-	(No symbol) [0x0xb89d86]
-	(No symbol) [0x0xb5b53e]
-	(No symbol) [0x0xb5c414]
-	GetHandleVerifier [0x0xf88a13+2457603]
-	GetHandleVerifier [0x0xf839d2+2437058]
-	GetHandleVerifier [0x0xd697f2+232930]
-	GetHandleVerifier [0x0xd59a18+167944]
-	GetHandleVerifier [0x0xd6092d+196381]
-	GetHandleVerifier [0x0xd48ee8+99544]
-	GetHandleVerifier [0x0xd49082+99954]
-	GetHandleVerifier [0x0xd3322a+10266]
-	BaseThreadInitThunk [0x0x761f5d49+25]
-	RtlInitializeExceptionChain [0x0x7725d6db+107]
-	RtlGetAppContainerNamedObjectPath [0x0x7725d661+561]
-</t>
-        </is>
+      <c r="E17" t="n">
+        <v>95.67</v>
       </c>
       <c r="F17" t="n">
         <v>84.98999999999999</v>
@@ -1217,7 +1113,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>57.98</v>
+        <v>87.55</v>
       </c>
       <c r="F22" t="n">
         <v>91.48999999999999</v>
@@ -3582,7 +3478,7 @@
         <v>79.98</v>
       </c>
       <c r="E87" t="n">
-        <v>79.98</v>
+        <v>79.97</v>
       </c>
       <c r="F87" t="n">
         <v>88.98999999999999</v>
